--- a/Product_Source/厂家直售510T起重机吊钩行车钩头防脱钩加厚钢丝绳电动葫芦吊钩/厂家直售510T起重机吊钩行车钩头防脱钩加厚钢丝绳电动葫芦吊钩.xlsx
+++ b/Product_Source/厂家直售510T起重机吊钩行车钩头防脱钩加厚钢丝绳电动葫芦吊钩/厂家直售510T起重机吊钩行车钩头防脱钩加厚钢丝绳电动葫芦吊钩.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\Data\1688\厂家直售510T起重机吊钩行车钩头防脱钩加厚钢丝绳电动葫芦吊钩\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\technological-trappist\Product_Source\厂家直售510T起重机吊钩行车钩头防脱钩加厚钢丝绳电动葫芦吊钩\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11CD035-5A2D-45B8-90B8-B02AF30C3CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5014BD40-07C2-4277-85CC-D7FA8C4334BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
   <si>
     <t>产品规格</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>价格 | 库存(个)</t>
-  </si>
-  <si>
-    <t>进货数量</t>
   </si>
   <si>
     <t>1吨吊钩</t>
@@ -409,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
@@ -418,7 +415,7 @@
     <col min="6" max="7" width="13.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,25 +437,22 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -467,21 +461,21 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -490,21 +484,21 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -513,21 +507,21 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -536,21 +530,21 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -559,21 +553,21 @@
         <v>621</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>16</v>
@@ -582,21 +576,21 @@
         <v>765</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>20</v>
